--- a/outputs/HubStor_NonDisc_Migration_Analysis.xlsx
+++ b/outputs/HubStor_NonDisc_Migration_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/245becee0fb282ce/Documents/Abhijit/AI and I/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_DB32B960E00AFAB0EA8B8B70E35F57E988FEFFB8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCBFDE86-A8E6-4987-A90E-FFBABD24C1E0}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_DB32B960E00AFAB0EA8B8B70E35F57E988FEFFB8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06197C55-597A-4CB8-9675-7C9EA94B91EB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
@@ -2342,460 +2342,460 @@
   </cellStyleXfs>
   <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="31" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="31" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="32" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="32" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="21" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="31" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="31" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="32" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="32" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="31" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="31" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="33" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2883,6 +2883,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3071,7 +3075,7 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="2" max="2" width="53.6640625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="25.109375" customWidth="1"/>
     <col min="5" max="6" width="17" customWidth="1"/>
@@ -3080,331 +3084,331 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="C3" s="142"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="142"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="142"/>
     </row>
     <row r="4" spans="2:7" ht="4.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="140"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
     </row>
     <row r="11" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="17">
         <v>25022.62</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="18">
         <v>24.436152343749999</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="19">
         <v>1716.22</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="20">
         <v>0.160149827273118</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="23">
         <v>0</v>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="24">
         <v>0</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="25">
         <v>0</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="29">
         <v>914.1</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="30">
         <v>0.89267578125000002</v>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="31">
         <v>34.4</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="32">
         <v>3.2100511928512898E-3</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="23">
         <v>195536.23</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="24">
         <v>190.95334960937501</v>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="25">
         <v>5930.68</v>
       </c>
-      <c r="G15" s="38">
+      <c r="G15" s="26">
         <v>0.55342402350056097</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="29">
         <v>525.59</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="30">
         <v>0.51327148437500003</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="31">
         <v>15.72</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="32">
         <v>1.4669187427797201E-3</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="23">
         <v>25098.77</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="24">
         <v>24.510517578125</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="25">
         <v>810.99</v>
       </c>
-      <c r="G17" s="38">
+      <c r="G17" s="26">
         <v>7.5677890025885694E-2</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="29">
         <v>72998.02</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="30">
         <v>71.287128906250004</v>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="31">
         <v>2208.33</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="32">
         <v>0.206071289264805</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="46">
+      <c r="C19" s="33"/>
+      <c r="D19" s="34">
         <v>320095.33</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="35">
         <v>312.59309570312502</v>
       </c>
-      <c r="F19" s="48">
+      <c r="F19" s="36">
         <v>10716.34</v>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="37">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="143" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
+      <c r="C21" s="143"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="143"/>
+      <c r="F21" s="143"/>
+      <c r="G21" s="143"/>
     </row>
     <row r="22" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="144" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="C22" s="144"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="144"/>
+      <c r="G22" s="144"/>
     </row>
     <row r="24" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="140"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="140"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="43">
+      <c r="C25" s="31">
         <v>479.77352991420003</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="25">
         <v>520</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="43">
+      <c r="C27" s="31">
         <v>48</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="37">
+      <c r="C28" s="25">
         <v>40</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="43">
+      <c r="C29" s="31">
         <v>40</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="50" t="s">
+      <c r="B30" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="39">
         <v>1127.7735299142</v>
       </c>
     </row>
@@ -3439,657 +3443,657 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="145" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="146" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="40">
         <v>0</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="41" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="42">
         <v>4887.87</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="41" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="42">
         <v>14645.59</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="53" t="s">
+      <c r="F8" s="41" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="40">
         <v>0</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="41" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="42">
         <v>300561.87</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="41" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="42">
         <v>1.0740000000000001</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="53" t="s">
+      <c r="F11" s="41" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="42">
         <v>320095.33</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="41" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="42">
         <v>312.59309570312502</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="53" t="s">
+      <c r="F13" s="41" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="42">
         <v>294470.96999999997</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="53" t="s">
+      <c r="F14" s="41" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="42">
         <v>25624.36</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="53" t="s">
+      <c r="F15" s="41" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="42">
         <v>25022.62</v>
       </c>
-      <c r="E16" s="33" t="s">
+      <c r="E16" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="53" t="s">
+      <c r="F16" s="41" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="146" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="C18" s="146"/>
+      <c r="D18" s="146"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="146"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E19" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F19" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="40">
         <v>3000</v>
       </c>
-      <c r="E20" s="33" t="s">
+      <c r="E20" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="53" t="s">
+      <c r="F20" s="41" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="54">
+      <c r="D21" s="42">
         <v>320095.33</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="53" t="s">
+      <c r="F21" s="41" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="54">
+      <c r="D22" s="42">
         <v>1066704.6399999999</v>
       </c>
-      <c r="E22" s="33" t="s">
+      <c r="E22" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="53" t="s">
+      <c r="F22" s="41" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="43">
         <v>0.30009999999999998</v>
       </c>
-      <c r="E23" s="33" t="s">
+      <c r="E23" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="53" t="s">
+      <c r="F23" s="41" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="40">
         <v>900</v>
       </c>
-      <c r="E24" s="33" t="s">
+      <c r="E24" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="F24" s="53" t="s">
+      <c r="F24" s="41" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="54">
+      <c r="D25" s="42">
         <v>11616.34</v>
       </c>
-      <c r="E25" s="33" t="s">
+      <c r="E25" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="F25" s="53" t="s">
+      <c r="F25" s="41" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="146" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+      <c r="C27" s="146"/>
+      <c r="D27" s="146"/>
+      <c r="E27" s="146"/>
+      <c r="F27" s="146"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="26" t="s">
+      <c r="F28" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="55">
+      <c r="D29" s="43">
         <v>2E-3</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="F29" s="53" t="s">
+      <c r="F29" s="41" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="D30" s="55">
+      <c r="D30" s="43">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="E30" s="33" t="s">
+      <c r="E30" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F30" s="53" t="s">
+      <c r="F30" s="41" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="33" t="s">
+      <c r="B31" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="55">
+      <c r="D31" s="43">
         <v>0.01</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F31" s="53" t="s">
+      <c r="F31" s="41" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="33" t="s">
+      <c r="B32" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D32" s="55">
+      <c r="D32" s="43">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="E32" s="33" t="s">
+      <c r="E32" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F32" s="53" t="s">
+      <c r="F32" s="41" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="33" t="s">
+      <c r="B33" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="D33" s="55">
+      <c r="D33" s="43">
         <v>0.05</v>
       </c>
-      <c r="E33" s="33" t="s">
+      <c r="E33" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F33" s="53" t="s">
+      <c r="F33" s="41" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="D34" s="54">
+      <c r="D34" s="42">
         <v>10716.34</v>
       </c>
-      <c r="E34" s="33" t="s">
+      <c r="E34" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="F34" s="53" t="s">
+      <c r="F34" s="41" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="146" t="s">
         <v>118</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
+      <c r="C36" s="146"/>
+      <c r="D36" s="146"/>
+      <c r="E36" s="146"/>
+      <c r="F36" s="146"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="26" t="s">
+      <c r="D37" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E37" s="26" t="s">
+      <c r="E37" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="F37" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="33" t="s">
+      <c r="B38" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C38" s="33" t="s">
+      <c r="C38" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="D38" s="55">
+      <c r="D38" s="43">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="E38" s="33" t="s">
+      <c r="E38" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="F38" s="53" t="s">
+      <c r="F38" s="41" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="33" t="s">
+      <c r="B39" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="33" t="s">
+      <c r="C39" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="D39" s="55">
+      <c r="D39" s="43">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="E39" s="33" t="s">
+      <c r="E39" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="F39" s="53" t="s">
+      <c r="F39" s="41" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="33" t="s">
+      <c r="B40" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C40" s="33" t="s">
+      <c r="C40" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="55">
+      <c r="D40" s="43">
         <v>9.8999999999999999E-4</v>
       </c>
-      <c r="E40" s="33" t="s">
+      <c r="E40" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="F40" s="53" t="s">
+      <c r="F40" s="41" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="33" t="s">
+      <c r="B41" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="C41" s="33" t="s">
+      <c r="C41" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="D41" s="55">
+      <c r="D41" s="43">
         <v>1E-3</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="F41" s="53" t="s">
+      <c r="F41" s="41" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="33" t="s">
+      <c r="B42" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="C42" s="33" t="s">
+      <c r="C42" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="D42" s="52">
+      <c r="D42" s="40">
         <v>130</v>
       </c>
-      <c r="E42" s="33" t="s">
+      <c r="E42" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="F42" s="53" t="s">
+      <c r="F42" s="41" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B43" s="33" t="s">
+      <c r="B43" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="C43" s="33" t="s">
+      <c r="C43" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="D43" s="52">
+      <c r="D43" s="40">
         <v>4</v>
       </c>
-      <c r="E43" s="33" t="s">
+      <c r="E43" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="F43" s="53" t="s">
+      <c r="F43" s="41" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="C44" s="33" t="s">
+      <c r="C44" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="D44" s="55">
+      <c r="D44" s="43">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="E44" s="33" t="s">
+      <c r="E44" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F44" s="53" t="s">
+      <c r="F44" s="41" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B45" s="33" t="s">
+      <c r="B45" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="C45" s="33" t="s">
+      <c r="C45" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="D45" s="55">
+      <c r="D45" s="43">
         <v>0.05</v>
       </c>
-      <c r="E45" s="33"/>
-      <c r="F45" s="53" t="s">
+      <c r="E45" s="21"/>
+      <c r="F45" s="41" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="33" t="s">
+      <c r="B46" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="33" t="s">
+      <c r="C46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="52">
+      <c r="D46" s="40">
         <v>300</v>
       </c>
-      <c r="E46" s="33" t="s">
+      <c r="E46" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="F46" s="53" t="s">
+      <c r="F46" s="41" t="s">
         <v>147</v>
       </c>
     </row>
@@ -4122,542 +4126,542 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="145" t="s">
         <v>148</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="140" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="14" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="27">
         <v>0</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="29">
         <v>0</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="27">
         <v>0</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" s="39" t="s">
+      <c r="G6" s="27" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="23">
         <v>4887.87</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="23">
         <v>5249.5723799999996</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="21">
         <v>0</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="21">
         <v>0</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="21" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="29">
         <v>14645.59</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="29">
         <v>15729.363660000001</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="31">
         <v>0.01</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="31">
         <v>157.29363660000001</v>
       </c>
-      <c r="G8" s="39" t="s">
+      <c r="G8" s="27" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="21">
         <v>0</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="23">
         <v>0</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="25">
         <v>0.03</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="25">
         <v>0</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="29">
         <v>300561.87</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="29">
         <v>322803.44838000002</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="31">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="31">
         <v>7101.6758643599997</v>
       </c>
-      <c r="G10" s="39" t="s">
+      <c r="G10" s="27" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="36">
         <v>7258.96950096</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="140" t="s">
         <v>163</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="140"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="14" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="29">
         <v>316261.82178</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="45">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="45">
         <v>0.05</v>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="31">
         <v>19494.391089000001</v>
       </c>
-      <c r="G15" s="58" t="s">
+      <c r="G15" s="46" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="23">
         <v>27520.56264</v>
       </c>
-      <c r="D16" s="59">
+      <c r="D16" s="47">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="E16" s="59">
+      <c r="E16" s="47">
         <v>0.05</v>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="25">
         <v>2315.5066991200001</v>
       </c>
-      <c r="G16" s="60" t="s">
+      <c r="G16" s="48" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="36">
         <v>21809.897788120001</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="140" t="s">
         <v>173</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="140"/>
+      <c r="E19" s="140"/>
+      <c r="F19" s="140"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="140"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26" t="s">
+      <c r="E20" s="14"/>
+      <c r="F20" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="14" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="C21" s="41">
+      <c r="C21" s="29">
         <v>343782.38442000002</v>
       </c>
-      <c r="D21" s="61">
+      <c r="D21" s="49">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="F21" s="43">
+      <c r="F21" s="31">
         <v>4297.2798052500002</v>
       </c>
-      <c r="G21" s="58" t="s">
+      <c r="G21" s="46" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="56" t="s">
+      <c r="B22" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="36">
         <v>4297.2798052500002</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="140" t="s">
         <v>181</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="140"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="140"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26" t="s">
+      <c r="E25" s="14"/>
+      <c r="F25" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="G25" s="14" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="C26" s="39">
+      <c r="C26" s="27">
         <v>4</v>
       </c>
-      <c r="D26" s="62">
+      <c r="D26" s="50">
         <v>500</v>
       </c>
-      <c r="F26" s="43">
+      <c r="F26" s="31">
         <v>2000</v>
       </c>
-      <c r="G26" s="58" t="s">
+      <c r="G26" s="46" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="21">
         <v>1</v>
       </c>
-      <c r="D27" s="63">
+      <c r="D27" s="51">
         <v>300</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="25">
         <v>300</v>
       </c>
-      <c r="G27" s="60" t="s">
+      <c r="G27" s="48" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="C28" s="39">
+      <c r="C28" s="27">
         <v>1</v>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="50">
         <v>500</v>
       </c>
-      <c r="F28" s="43">
+      <c r="F28" s="31">
         <v>500</v>
       </c>
-      <c r="G28" s="58" t="s">
+      <c r="G28" s="46" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="21">
         <v>1</v>
       </c>
-      <c r="D29" s="63">
+      <c r="D29" s="51">
         <v>500</v>
       </c>
-      <c r="F29" s="37">
+      <c r="F29" s="25">
         <v>500</v>
       </c>
-      <c r="G29" s="60" t="s">
+      <c r="G29" s="48" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="C30" s="39">
+      <c r="C30" s="27">
         <v>1</v>
       </c>
-      <c r="D30" s="62">
+      <c r="D30" s="50">
         <v>3000</v>
       </c>
-      <c r="F30" s="43">
+      <c r="F30" s="31">
         <v>3000</v>
       </c>
-      <c r="G30" s="58" t="s">
+      <c r="G30" s="46" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="33" t="s">
+      <c r="B31" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="21">
         <v>1</v>
       </c>
-      <c r="D31" s="63">
+      <c r="D31" s="51">
         <v>2000</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="25">
         <v>2000</v>
       </c>
-      <c r="G31" s="60" t="s">
+      <c r="G31" s="48" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="56" t="s">
+      <c r="B32" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="48">
+      <c r="F32" s="36">
         <v>8300</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="147" t="s">
         <v>198</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
+      <c r="C34" s="147"/>
+      <c r="D34" s="147"/>
+      <c r="E34" s="147"/>
+      <c r="F34" s="147"/>
+      <c r="G34" s="147"/>
+      <c r="H34" s="147"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="C35" s="43">
+      <c r="C35" s="31">
         <v>7258.96950096</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="33" t="s">
+      <c r="B36" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="25">
         <v>21809.897788120001</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="C37" s="43">
+      <c r="C37" s="31">
         <v>4297.2798052500002</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="33" t="s">
+      <c r="B38" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="C38" s="65">
+      <c r="C38" s="52">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="C39" s="43">
+      <c r="C39" s="31">
         <v>8300</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="33" t="s">
+      <c r="B40" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="C40" s="37">
+      <c r="C40" s="25">
         <v>4136.6147094329999</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="66" t="s">
+      <c r="B41" s="53" t="s">
         <v>205</v>
       </c>
-      <c r="C41" s="67">
+      <c r="C41" s="54">
         <v>45502.761803763002</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="140" t="s">
         <v>206</v>
       </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
+      <c r="C43" s="140"/>
+      <c r="D43" s="140"/>
+      <c r="E43" s="140"/>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="140"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="39" t="s">
+      <c r="B44" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="C44" s="68">
+      <c r="C44" s="55">
         <v>10488.5664700858</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="33" t="s">
+      <c r="B45" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="C45" s="69">
+      <c r="C45" s="56">
         <v>4.3383203923567999</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="39" t="s">
+      <c r="B46" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="C46" s="68">
+      <c r="C46" s="55">
         <v>125862.79764103</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="33" t="s">
+      <c r="B47" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="C47" s="70">
+      <c r="C47" s="57">
         <v>80360.035837266594</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="39" t="s">
+      <c r="B48" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="C48" s="68">
+      <c r="C48" s="55">
         <v>332085.63111932599</v>
       </c>
     </row>
@@ -4695,723 +4699,723 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="145" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="145"/>
+      <c r="K2" s="145"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="148" t="s">
         <v>213</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="148"/>
+      <c r="K3" s="148"/>
     </row>
     <row r="4" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="149" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
     </row>
     <row r="5" spans="2:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="I5" s="26" t="s">
+      <c r="I5" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="J5" s="26" t="s">
+      <c r="J5" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="K5" s="26" t="s">
+      <c r="K5" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="L5" s="26" t="s">
+      <c r="L5" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="M5" s="14" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="6" spans="2:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="58" t="s">
         <v>227</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="59" t="s">
         <v>228</v>
       </c>
-      <c r="D6" s="73" t="s">
+      <c r="D6" s="60" t="s">
         <v>229</v>
       </c>
-      <c r="E6" s="73" t="s">
+      <c r="E6" s="60" t="s">
         <v>230</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="60" t="s">
         <v>231</v>
       </c>
-      <c r="G6" s="74" t="s">
+      <c r="G6" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="74" t="s">
+      <c r="H6" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="I6" s="74" t="s">
+      <c r="I6" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="72" t="s">
+      <c r="J6" s="59" t="s">
         <v>232</v>
       </c>
-      <c r="K6" s="75" t="s">
+      <c r="K6" s="62" t="s">
         <v>233</v>
       </c>
-      <c r="L6" s="76" t="s">
+      <c r="L6" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="M6" s="76" t="s">
+      <c r="M6" s="63" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="71" t="s">
+      <c r="B7" s="58" t="s">
         <v>235</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="59" t="s">
         <v>236</v>
       </c>
-      <c r="D7" s="73" t="s">
+      <c r="D7" s="60" t="s">
         <v>237</v>
       </c>
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="60" t="s">
         <v>238</v>
       </c>
-      <c r="F7" s="73" t="s">
+      <c r="F7" s="60" t="s">
         <v>239</v>
       </c>
-      <c r="G7" s="77">
+      <c r="G7" s="64">
         <v>102.4</v>
       </c>
-      <c r="H7" s="78">
+      <c r="H7" s="65">
         <v>0.1</v>
       </c>
-      <c r="I7" s="74" t="s">
+      <c r="I7" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="72" t="s">
+      <c r="J7" s="59" t="s">
         <v>240</v>
       </c>
-      <c r="K7" s="75" t="s">
+      <c r="K7" s="62" t="s">
         <v>241</v>
       </c>
-      <c r="L7" s="76" t="s">
+      <c r="L7" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="M7" s="76" t="s">
+      <c r="M7" s="63" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="8" spans="2:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="58" t="s">
         <v>242</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="D8" s="73" t="s">
+      <c r="D8" s="60" t="s">
         <v>244</v>
       </c>
-      <c r="E8" s="73" t="s">
+      <c r="E8" s="60" t="s">
         <v>245</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="60" t="s">
         <v>231</v>
       </c>
-      <c r="G8" s="77">
+      <c r="G8" s="64">
         <v>25022.62</v>
       </c>
-      <c r="H8" s="78">
+      <c r="H8" s="65">
         <v>24.436152343749999</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="66">
         <v>1716.22</v>
       </c>
-      <c r="J8" s="72" t="s">
+      <c r="J8" s="59" t="s">
         <v>246</v>
       </c>
-      <c r="K8" s="75" t="s">
+      <c r="K8" s="62" t="s">
         <v>241</v>
       </c>
-      <c r="L8" s="80" t="s">
+      <c r="L8" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="M8" s="76" t="s">
+      <c r="M8" s="63" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="9" spans="2:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="68" t="s">
         <v>248</v>
       </c>
-      <c r="C9" s="82" t="s">
+      <c r="C9" s="69" t="s">
         <v>249</v>
       </c>
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="70" t="s">
         <v>250</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="70" t="s">
         <v>251</v>
       </c>
-      <c r="F9" s="83" t="s">
+      <c r="F9" s="70" t="s">
         <v>252</v>
       </c>
-      <c r="G9" s="84">
+      <c r="G9" s="71">
         <v>914.1</v>
       </c>
-      <c r="H9" s="85">
+      <c r="H9" s="72">
         <v>0.89267578125000002</v>
       </c>
-      <c r="I9" s="86">
+      <c r="I9" s="73">
         <v>34.4</v>
       </c>
-      <c r="J9" s="82" t="s">
+      <c r="J9" s="69" t="s">
         <v>253</v>
       </c>
-      <c r="K9" s="87" t="s">
+      <c r="K9" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="L9" s="88" t="s">
+      <c r="L9" s="75" t="s">
         <v>255</v>
       </c>
-      <c r="M9" s="89" t="s">
+      <c r="M9" s="76" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="10" spans="2:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="81" t="s">
+      <c r="B10" s="68" t="s">
         <v>256</v>
       </c>
-      <c r="C10" s="82" t="s">
+      <c r="C10" s="69" t="s">
         <v>257</v>
       </c>
-      <c r="D10" s="83" t="s">
+      <c r="D10" s="70" t="s">
         <v>258</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="70" t="s">
         <v>259</v>
       </c>
-      <c r="F10" s="83" t="s">
+      <c r="F10" s="70" t="s">
         <v>260</v>
       </c>
-      <c r="G10" s="84">
+      <c r="G10" s="71">
         <v>525.59</v>
       </c>
-      <c r="H10" s="85">
+      <c r="H10" s="72">
         <v>0.51327148437500003</v>
       </c>
-      <c r="I10" s="86">
+      <c r="I10" s="73">
         <v>15.72</v>
       </c>
-      <c r="J10" s="82" t="s">
+      <c r="J10" s="69" t="s">
         <v>261</v>
       </c>
-      <c r="K10" s="87" t="s">
+      <c r="K10" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="L10" s="88" t="s">
+      <c r="L10" s="75" t="s">
         <v>262</v>
       </c>
-      <c r="M10" s="89" t="s">
+      <c r="M10" s="76" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="81" t="s">
+      <c r="B11" s="68" t="s">
         <v>263</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="69" t="s">
         <v>264</v>
       </c>
-      <c r="D11" s="83" t="s">
+      <c r="D11" s="70" t="s">
         <v>265</v>
       </c>
-      <c r="E11" s="83" t="s">
+      <c r="E11" s="70" t="s">
         <v>266</v>
       </c>
-      <c r="F11" s="83" t="s">
+      <c r="F11" s="70" t="s">
         <v>252</v>
       </c>
-      <c r="G11" s="84">
+      <c r="G11" s="71">
         <v>25098.77</v>
       </c>
-      <c r="H11" s="85">
+      <c r="H11" s="72">
         <v>24.510517578125</v>
       </c>
-      <c r="I11" s="86">
+      <c r="I11" s="73">
         <v>810.99</v>
       </c>
-      <c r="J11" s="82" t="s">
+      <c r="J11" s="69" t="s">
         <v>267</v>
       </c>
-      <c r="K11" s="87" t="s">
+      <c r="K11" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="L11" s="88" t="s">
+      <c r="L11" s="75" t="s">
         <v>268</v>
       </c>
-      <c r="M11" s="89" t="s">
+      <c r="M11" s="76" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="90" t="s">
+      <c r="B12" s="77" t="s">
         <v>269</v>
       </c>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="78" t="s">
         <v>270</v>
       </c>
-      <c r="D12" s="92" t="s">
+      <c r="D12" s="79" t="s">
         <v>271</v>
       </c>
-      <c r="E12" s="92" t="s">
+      <c r="E12" s="79" t="s">
         <v>247</v>
       </c>
-      <c r="F12" s="92" t="s">
+      <c r="F12" s="79" t="s">
         <v>252</v>
       </c>
-      <c r="G12" s="93">
+      <c r="G12" s="80">
         <v>195536.23</v>
       </c>
-      <c r="H12" s="94">
+      <c r="H12" s="81">
         <v>190.95334960937501</v>
       </c>
-      <c r="I12" s="95">
+      <c r="I12" s="82">
         <v>5930.68</v>
       </c>
-      <c r="J12" s="91" t="s">
+      <c r="J12" s="78" t="s">
         <v>272</v>
       </c>
-      <c r="K12" s="96" t="s">
+      <c r="K12" s="83" t="s">
         <v>254</v>
       </c>
-      <c r="L12" s="97" t="s">
+      <c r="L12" s="84" t="s">
         <v>273</v>
       </c>
-      <c r="M12" s="98" t="s">
+      <c r="M12" s="85" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="13" spans="2:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="77" t="s">
         <v>274</v>
       </c>
-      <c r="C13" s="91" t="s">
+      <c r="C13" s="78" t="s">
         <v>275</v>
       </c>
-      <c r="D13" s="92" t="s">
+      <c r="D13" s="79" t="s">
         <v>276</v>
       </c>
-      <c r="E13" s="92" t="s">
+      <c r="E13" s="79" t="s">
         <v>255</v>
       </c>
-      <c r="F13" s="92" t="s">
+      <c r="F13" s="79" t="s">
         <v>252</v>
       </c>
-      <c r="G13" s="93">
+      <c r="G13" s="80">
         <v>72998.02</v>
       </c>
-      <c r="H13" s="94">
+      <c r="H13" s="81">
         <v>71.287128906250004</v>
       </c>
-      <c r="I13" s="95">
+      <c r="I13" s="82">
         <v>2208.33</v>
       </c>
-      <c r="J13" s="91" t="s">
+      <c r="J13" s="78" t="s">
         <v>277</v>
       </c>
-      <c r="K13" s="96" t="s">
+      <c r="K13" s="83" t="s">
         <v>254</v>
       </c>
-      <c r="L13" s="97" t="s">
+      <c r="L13" s="84" t="s">
         <v>278</v>
       </c>
-      <c r="M13" s="98" t="s">
+      <c r="M13" s="85" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="14" spans="2:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="99" t="s">
+      <c r="B14" s="86" t="s">
         <v>279</v>
       </c>
-      <c r="C14" s="100" t="s">
+      <c r="C14" s="87" t="s">
         <v>280</v>
       </c>
-      <c r="D14" s="101" t="s">
+      <c r="D14" s="88" t="s">
         <v>281</v>
       </c>
-      <c r="E14" s="101" t="s">
+      <c r="E14" s="88" t="s">
         <v>262</v>
       </c>
-      <c r="F14" s="101" t="s">
+      <c r="F14" s="88" t="s">
         <v>260</v>
       </c>
-      <c r="G14" s="102" t="s">
+      <c r="G14" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="H14" s="102" t="s">
+      <c r="H14" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="102" t="s">
+      <c r="I14" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="J14" s="100" t="s">
+      <c r="J14" s="87" t="s">
         <v>282</v>
       </c>
-      <c r="K14" s="103" t="s">
+      <c r="K14" s="90" t="s">
         <v>283</v>
       </c>
-      <c r="L14" s="104" t="s">
+      <c r="L14" s="91" t="s">
         <v>77</v>
       </c>
-      <c r="M14" s="104" t="s">
+      <c r="M14" s="91" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="15" spans="2:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="105" t="s">
+      <c r="B15" s="92" t="s">
         <v>284</v>
       </c>
-      <c r="C15" s="106" t="s">
+      <c r="C15" s="93" t="s">
         <v>285</v>
       </c>
-      <c r="D15" s="107" t="s">
+      <c r="D15" s="94" t="s">
         <v>286</v>
       </c>
-      <c r="E15" s="107" t="s">
+      <c r="E15" s="94" t="s">
         <v>278</v>
       </c>
-      <c r="F15" s="107" t="s">
+      <c r="F15" s="94" t="s">
         <v>287</v>
       </c>
-      <c r="G15" s="108" t="s">
+      <c r="G15" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="H15" s="108" t="s">
+      <c r="H15" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="108" t="s">
+      <c r="I15" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="J15" s="106" t="s">
+      <c r="J15" s="93" t="s">
         <v>288</v>
       </c>
-      <c r="K15" s="109" t="s">
+      <c r="K15" s="96" t="s">
         <v>289</v>
       </c>
-      <c r="L15" s="110" t="s">
+      <c r="L15" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="M15" s="110" t="s">
+      <c r="M15" s="97" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="16" spans="2:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="105" t="s">
+      <c r="B16" s="92" t="s">
         <v>290</v>
       </c>
-      <c r="C16" s="106" t="s">
+      <c r="C16" s="93" t="s">
         <v>291</v>
       </c>
-      <c r="D16" s="107" t="s">
+      <c r="D16" s="94" t="s">
         <v>292</v>
       </c>
-      <c r="E16" s="107" t="s">
+      <c r="E16" s="94" t="s">
         <v>293</v>
       </c>
-      <c r="F16" s="107" t="s">
+      <c r="F16" s="94" t="s">
         <v>260</v>
       </c>
-      <c r="G16" s="108" t="s">
+      <c r="G16" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="108" t="s">
+      <c r="H16" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="108" t="s">
+      <c r="I16" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="J16" s="106" t="s">
+      <c r="J16" s="93" t="s">
         <v>294</v>
       </c>
-      <c r="K16" s="109" t="s">
+      <c r="K16" s="96" t="s">
         <v>295</v>
       </c>
-      <c r="L16" s="110" t="s">
+      <c r="L16" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="M16" s="110" t="s">
+      <c r="M16" s="97" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="150" t="s">
         <v>296</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
+      <c r="C18" s="150"/>
+      <c r="D18" s="150"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="150"/>
+      <c r="G18" s="150"/>
+      <c r="H18" s="150"/>
+      <c r="I18" s="150"/>
+      <c r="J18" s="150"/>
+      <c r="K18" s="150"/>
+      <c r="L18" s="150"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E19" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F19" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G19" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="H19" s="26" t="s">
+      <c r="H19" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="I19" s="26" t="s">
+      <c r="I19" s="14" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="27" t="s">
         <v>303</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="F20" s="111" t="s">
+      <c r="F20" s="98" t="s">
         <v>247</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="H20" s="39" t="s">
+      <c r="H20" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="I20" s="39" t="s">
+      <c r="I20" s="27" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="F21" s="112" t="s">
+      <c r="F21" s="99" t="s">
         <v>255</v>
       </c>
-      <c r="G21" s="33" t="s">
+      <c r="G21" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="H21" s="33" t="s">
+      <c r="H21" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="I21" s="33" t="s">
+      <c r="I21" s="21" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="27" t="s">
         <v>308</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D22" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="E22" s="39" t="s">
+      <c r="E22" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="F22" s="111" t="s">
+      <c r="F22" s="98" t="s">
         <v>262</v>
       </c>
-      <c r="G22" s="39" t="s">
+      <c r="G22" s="27" t="s">
         <v>262</v>
       </c>
-      <c r="H22" s="39" t="s">
+      <c r="H22" s="27" t="s">
         <v>262</v>
       </c>
-      <c r="I22" s="39" t="s">
+      <c r="I22" s="27" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="D23" s="33" t="s">
+      <c r="D23" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="E23" s="33" t="s">
+      <c r="E23" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="F23" s="112" t="s">
+      <c r="F23" s="99" t="s">
         <v>268</v>
       </c>
-      <c r="G23" s="33" t="s">
+      <c r="G23" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="H23" s="33" t="s">
+      <c r="H23" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="I23" s="33" t="s">
+      <c r="I23" s="21" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="27" t="s">
         <v>313</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="27" t="s">
         <v>303</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="D24" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E24" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="F24" s="111" t="s">
+      <c r="F24" s="98" t="s">
         <v>273</v>
       </c>
-      <c r="G24" s="39" t="s">
+      <c r="G24" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="H24" s="39" t="s">
+      <c r="H24" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="I24" s="39" t="s">
+      <c r="I24" s="27" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="D25" s="33" t="s">
+      <c r="D25" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="E25" s="33" t="s">
+      <c r="E25" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="F25" s="112" t="s">
+      <c r="F25" s="99" t="s">
         <v>278</v>
       </c>
-      <c r="G25" s="33" t="s">
+      <c r="G25" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="H25" s="33" t="s">
+      <c r="H25" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="I25" s="33" t="s">
+      <c r="I25" s="21" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="113" t="s">
+      <c r="B26" s="100" t="s">
         <v>318</v>
       </c>
-      <c r="C26" s="113" t="s">
+      <c r="C26" s="100" t="s">
         <v>319</v>
       </c>
-      <c r="D26" s="113" t="s">
+      <c r="D26" s="100" t="s">
         <v>255</v>
       </c>
-      <c r="E26" s="113" t="s">
+      <c r="E26" s="100" t="s">
         <v>304</v>
       </c>
-      <c r="F26" s="113" t="s">
+      <c r="F26" s="100" t="s">
         <v>293</v>
       </c>
-      <c r="G26" s="113" t="s">
+      <c r="G26" s="100" t="s">
         <v>293</v>
       </c>
-      <c r="H26" s="113" t="s">
+      <c r="H26" s="100" t="s">
         <v>293</v>
       </c>
-      <c r="I26" s="113" t="s">
+      <c r="I26" s="100" t="s">
         <v>320</v>
       </c>
     </row>
@@ -5442,436 +5446,436 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="151" t="s">
         <v>321</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="151"/>
+      <c r="K2" s="151"/>
+      <c r="L2" s="151"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="151"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="148" t="s">
         <v>322</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="148"/>
+      <c r="K3" s="148"/>
+      <c r="L3" s="148"/>
+      <c r="M3" s="148"/>
+      <c r="N3" s="148"/>
     </row>
     <row r="4" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="152" t="s">
         <v>323</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="114" t="s">
+      <c r="B5" s="101" t="s">
         <v>324</v>
       </c>
-      <c r="C5" s="115">
+      <c r="C5" s="102">
         <v>11616.34</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="114" t="s">
+      <c r="B6" s="101" t="s">
         <v>325</v>
       </c>
-      <c r="C6" s="115">
+      <c r="C6" s="102">
         <v>1127.7735299142</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="114" t="s">
+      <c r="B7" s="101" t="s">
         <v>326</v>
       </c>
-      <c r="C7" s="115">
+      <c r="C7" s="102">
         <v>45502.761803763002</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="116" t="s">
+      <c r="C9" s="103" t="s">
         <v>328</v>
       </c>
-      <c r="D9" s="116" t="s">
+      <c r="D9" s="103" t="s">
         <v>329</v>
       </c>
-      <c r="E9" s="116" t="s">
+      <c r="E9" s="103" t="s">
         <v>330</v>
       </c>
-      <c r="F9" s="116" t="s">
+      <c r="F9" s="103" t="s">
         <v>331</v>
       </c>
-      <c r="G9" s="116" t="s">
+      <c r="G9" s="103" t="s">
         <v>332</v>
       </c>
-      <c r="H9" s="116" t="s">
+      <c r="H9" s="103" t="s">
         <v>333</v>
       </c>
-      <c r="I9" s="116" t="s">
+      <c r="I9" s="103" t="s">
         <v>334</v>
       </c>
-      <c r="J9" s="116" t="s">
+      <c r="J9" s="103" t="s">
         <v>335</v>
       </c>
-      <c r="K9" s="116" t="s">
+      <c r="K9" s="103" t="s">
         <v>336</v>
       </c>
-      <c r="L9" s="116" t="s">
+      <c r="L9" s="103" t="s">
         <v>337</v>
       </c>
-      <c r="M9" s="116" t="s">
+      <c r="M9" s="103" t="s">
         <v>338</v>
       </c>
-      <c r="N9" s="116" t="s">
+      <c r="N9" s="103" t="s">
         <v>339</v>
       </c>
-      <c r="O9" s="26" t="s">
+      <c r="O9" s="14" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="117" t="s">
+      <c r="B10" s="104" t="s">
         <v>341</v>
       </c>
-      <c r="C10" s="118">
+      <c r="C10" s="105">
         <v>11616.34</v>
       </c>
-      <c r="D10" s="118">
+      <c r="D10" s="105">
         <v>11616.34</v>
       </c>
-      <c r="E10" s="118">
+      <c r="E10" s="105">
         <v>11616.34</v>
       </c>
-      <c r="F10" s="118">
+      <c r="F10" s="105">
         <v>11616.34</v>
       </c>
-      <c r="G10" s="118">
+      <c r="G10" s="105">
         <v>11616.34</v>
       </c>
-      <c r="H10" s="118">
+      <c r="H10" s="105">
         <v>9900.1200000000008</v>
       </c>
-      <c r="I10" s="118">
+      <c r="I10" s="105">
         <v>9850</v>
       </c>
-      <c r="J10" s="118">
+      <c r="J10" s="105">
         <v>3108.33</v>
       </c>
-      <c r="K10" s="118">
+      <c r="K10" s="105">
         <v>900</v>
       </c>
-      <c r="L10" s="118">
+      <c r="L10" s="105">
         <v>900</v>
       </c>
-      <c r="M10" s="118">
+      <c r="M10" s="105">
         <v>900</v>
       </c>
-      <c r="N10" s="118">
+      <c r="N10" s="105">
         <v>900</v>
       </c>
-      <c r="O10" s="119">
+      <c r="O10" s="106">
         <v>84540.15</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="120" t="s">
+      <c r="B11" s="107" t="s">
         <v>342</v>
       </c>
-      <c r="C11" s="121">
+      <c r="C11" s="108">
         <v>0</v>
       </c>
-      <c r="D11" s="121">
+      <c r="D11" s="108">
         <v>0</v>
       </c>
-      <c r="E11" s="121">
+      <c r="E11" s="108">
         <v>295.505048027729</v>
       </c>
-      <c r="F11" s="121">
+      <c r="F11" s="108">
         <v>426.87514294193602</v>
       </c>
-      <c r="G11" s="121">
+      <c r="G11" s="108">
         <v>725.28210642057297</v>
       </c>
-      <c r="H11" s="121">
+      <c r="H11" s="108">
         <v>1387.7735299142</v>
       </c>
-      <c r="I11" s="121">
+      <c r="I11" s="108">
         <v>1387.7735299142</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="108">
         <v>1387.7735299142</v>
       </c>
-      <c r="K11" s="121">
+      <c r="K11" s="108">
         <v>1387.7735299142</v>
       </c>
-      <c r="L11" s="121">
+      <c r="L11" s="108">
         <v>1387.7735299142</v>
       </c>
-      <c r="M11" s="121">
+      <c r="M11" s="108">
         <v>1387.7735299142</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="108">
         <v>1387.7735299142</v>
       </c>
-      <c r="O11" s="122">
+      <c r="O11" s="109">
         <v>11162.077006789599</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="C12" s="123">
+      <c r="C12" s="110">
         <v>18201.104721505199</v>
       </c>
-      <c r="D12" s="123">
+      <c r="D12" s="110">
         <v>18201.104721505199</v>
       </c>
-      <c r="E12" s="123">
+      <c r="E12" s="110">
         <v>9100.5523607525993</v>
       </c>
-      <c r="F12" s="123">
+      <c r="F12" s="110">
         <v>0</v>
       </c>
-      <c r="G12" s="123">
+      <c r="G12" s="110">
         <v>0</v>
       </c>
-      <c r="H12" s="123">
+      <c r="H12" s="110">
         <v>0</v>
       </c>
-      <c r="I12" s="123">
+      <c r="I12" s="110">
         <v>0</v>
       </c>
-      <c r="J12" s="123">
+      <c r="J12" s="110">
         <v>0</v>
       </c>
-      <c r="K12" s="123">
+      <c r="K12" s="110">
         <v>0</v>
       </c>
-      <c r="L12" s="123">
+      <c r="L12" s="110">
         <v>0</v>
       </c>
-      <c r="M12" s="123">
+      <c r="M12" s="110">
         <v>0</v>
       </c>
-      <c r="N12" s="123">
+      <c r="N12" s="110">
         <v>0</v>
       </c>
-      <c r="O12" s="124">
+      <c r="O12" s="111">
         <v>45502.761803763002</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="44" t="s">
         <v>344</v>
       </c>
-      <c r="C13" s="125">
+      <c r="C13" s="112">
         <v>29817.444721505199</v>
       </c>
-      <c r="D13" s="125">
+      <c r="D13" s="112">
         <v>29817.444721505199</v>
       </c>
-      <c r="E13" s="125">
+      <c r="E13" s="112">
         <v>21012.3974087803</v>
       </c>
-      <c r="F13" s="125">
+      <c r="F13" s="112">
         <v>12043.215142941899</v>
       </c>
-      <c r="G13" s="125">
+      <c r="G13" s="112">
         <v>12341.6221064206</v>
       </c>
-      <c r="H13" s="125">
+      <c r="H13" s="112">
         <v>11287.893529914199</v>
       </c>
-      <c r="I13" s="125">
+      <c r="I13" s="112">
         <v>11237.7735299142</v>
       </c>
-      <c r="J13" s="125">
+      <c r="J13" s="112">
         <v>4496.1035299142004</v>
       </c>
-      <c r="K13" s="125">
+      <c r="K13" s="112">
         <v>2287.7735299142</v>
       </c>
-      <c r="L13" s="125">
+      <c r="L13" s="112">
         <v>2287.7735299142</v>
       </c>
-      <c r="M13" s="125">
+      <c r="M13" s="112">
         <v>2287.7735299142</v>
       </c>
-      <c r="N13" s="125">
+      <c r="N13" s="112">
         <v>2287.7735299142</v>
       </c>
-      <c r="O13" s="126">
+      <c r="O13" s="113">
         <v>141204.98881055301</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="120" t="s">
+      <c r="B14" s="107" t="s">
         <v>345</v>
       </c>
-      <c r="C14" s="127">
+      <c r="C14" s="114">
         <v>-18201.104721505199</v>
       </c>
-      <c r="D14" s="127">
+      <c r="D14" s="114">
         <v>-18201.104721505199</v>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="114">
         <v>-9396.0574087803307</v>
       </c>
-      <c r="F14" s="127">
+      <c r="F14" s="114">
         <v>-426.875142941935</v>
       </c>
-      <c r="G14" s="127">
+      <c r="G14" s="114">
         <v>-725.28210642057297</v>
       </c>
-      <c r="H14" s="128">
+      <c r="H14" s="115">
         <v>328.44647008579898</v>
       </c>
-      <c r="I14" s="128">
+      <c r="I14" s="115">
         <v>378.56647008580001</v>
       </c>
-      <c r="J14" s="128">
+      <c r="J14" s="115">
         <v>7120.2364700857997</v>
       </c>
-      <c r="K14" s="128">
+      <c r="K14" s="115">
         <v>9328.5664700857997</v>
       </c>
-      <c r="L14" s="128">
+      <c r="L14" s="115">
         <v>9328.5664700857997</v>
       </c>
-      <c r="M14" s="128">
+      <c r="M14" s="115">
         <v>9328.5664700857997</v>
       </c>
-      <c r="N14" s="128">
+      <c r="N14" s="115">
         <v>9328.5664700857997</v>
       </c>
-      <c r="O14" s="129">
+      <c r="O14" s="116">
         <v>-1808.90881055265</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="130" t="s">
+      <c r="B15" s="117" t="s">
         <v>346</v>
       </c>
-      <c r="C15" s="131">
+      <c r="C15" s="118">
         <v>-18201.104721505199</v>
       </c>
-      <c r="D15" s="131">
+      <c r="D15" s="118">
         <v>-36402.209443010397</v>
       </c>
-      <c r="E15" s="131">
+      <c r="E15" s="118">
         <v>-45798.2668517907</v>
       </c>
-      <c r="F15" s="131">
+      <c r="F15" s="118">
         <v>-46225.141994732701</v>
       </c>
-      <c r="G15" s="131">
+      <c r="G15" s="118">
         <v>-46950.424101153301</v>
       </c>
-      <c r="H15" s="131">
+      <c r="H15" s="118">
         <v>-46621.977631067501</v>
       </c>
-      <c r="I15" s="131">
+      <c r="I15" s="118">
         <v>-46243.411160981697</v>
       </c>
-      <c r="J15" s="131">
+      <c r="J15" s="118">
         <v>-39123.174690895801</v>
       </c>
-      <c r="K15" s="131">
+      <c r="K15" s="118">
         <v>-29794.6082208101</v>
       </c>
-      <c r="L15" s="131">
+      <c r="L15" s="118">
         <v>-20466.0417507243</v>
       </c>
-      <c r="M15" s="131">
+      <c r="M15" s="118">
         <v>-11137.4752806385</v>
       </c>
-      <c r="N15" s="131">
+      <c r="N15" s="118">
         <v>-1808.90881055265</v>
       </c>
-      <c r="O15" s="132">
+      <c r="O15" s="119">
         <v>-1808.90881055265</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="140" t="s">
         <v>347</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="140"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="140"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="E18" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="F18" s="14" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="133" t="s">
+      <c r="B19" s="120" t="s">
         <v>353</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="D19" s="62">
+      <c r="D19" s="50">
         <v>80940.149999999994</v>
       </c>
-      <c r="E19" s="62">
+      <c r="E19" s="50">
         <v>51113.744690895903</v>
       </c>
-      <c r="F19" s="134">
+      <c r="F19" s="121">
         <v>29826.405309104099</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="135" t="s">
+      <c r="B20" s="122" t="s">
         <v>355</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="D20" s="63">
+      <c r="D20" s="51">
         <v>3600</v>
       </c>
-      <c r="E20" s="63">
+      <c r="E20" s="51">
         <v>5551.0941196568001</v>
       </c>
-      <c r="F20" s="136">
+      <c r="F20" s="123">
         <v>-1951.0941196568001</v>
       </c>
     </row>
@@ -5905,1347 +5909,1352 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="145" t="s">
         <v>357</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="14" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="140" t="s">
         <v>363</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
     </row>
     <row r="6" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="137" t="s">
+      <c r="B6" s="124" t="s">
         <v>364</v>
       </c>
-      <c r="C6" s="138" t="s">
+      <c r="C6" s="125" t="s">
         <v>365</v>
       </c>
-      <c r="D6" s="139" t="s">
+      <c r="D6" s="126" t="s">
         <v>366</v>
       </c>
-      <c r="E6" s="58" t="s">
+      <c r="E6" s="46" t="s">
         <v>367</v>
       </c>
-      <c r="F6" s="139" t="s">
+      <c r="F6" s="126" t="s">
         <v>368</v>
       </c>
-      <c r="G6" s="140" t="s">
+      <c r="G6" s="127" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="141" t="s">
+      <c r="B7" s="128" t="s">
         <v>364</v>
       </c>
-      <c r="C7" s="142" t="s">
+      <c r="C7" s="129" t="s">
         <v>370</v>
       </c>
-      <c r="D7" s="143" t="s">
+      <c r="D7" s="130" t="s">
         <v>371</v>
       </c>
-      <c r="E7" s="60" t="s">
+      <c r="E7" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="F7" s="143" t="s">
+      <c r="F7" s="130" t="s">
         <v>372</v>
       </c>
-      <c r="G7" s="140" t="s">
+      <c r="G7" s="127" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="124" t="s">
         <v>364</v>
       </c>
-      <c r="C8" s="138" t="s">
+      <c r="C8" s="125" t="s">
         <v>370</v>
       </c>
-      <c r="D8" s="139" t="s">
+      <c r="D8" s="126" t="s">
         <v>374</v>
       </c>
-      <c r="E8" s="58" t="s">
+      <c r="E8" s="46" t="s">
         <v>283</v>
       </c>
-      <c r="F8" s="139" t="s">
+      <c r="F8" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="G8" s="140" t="s">
+      <c r="G8" s="127" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="141" t="s">
+      <c r="B9" s="128" t="s">
         <v>377</v>
       </c>
-      <c r="C9" s="142" t="s">
+      <c r="C9" s="129" t="s">
         <v>370</v>
       </c>
-      <c r="D9" s="143" t="s">
+      <c r="D9" s="130" t="s">
         <v>378</v>
       </c>
-      <c r="E9" s="60" t="s">
+      <c r="E9" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="F9" s="143" t="s">
+      <c r="F9" s="130" t="s">
         <v>379</v>
       </c>
-      <c r="G9" s="140" t="s">
+      <c r="G9" s="127" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="137" t="s">
+      <c r="B10" s="124" t="s">
         <v>377</v>
       </c>
-      <c r="C10" s="138" t="s">
+      <c r="C10" s="125" t="s">
         <v>381</v>
       </c>
-      <c r="D10" s="139" t="s">
+      <c r="D10" s="126" t="s">
         <v>382</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="46" t="s">
         <v>283</v>
       </c>
-      <c r="F10" s="139" t="s">
+      <c r="F10" s="126" t="s">
         <v>383</v>
       </c>
-      <c r="G10" s="140" t="s">
+      <c r="G10" s="127" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="141" t="s">
+      <c r="B11" s="128" t="s">
         <v>377</v>
       </c>
-      <c r="C11" s="142" t="s">
+      <c r="C11" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="D11" s="143" t="s">
+      <c r="D11" s="130" t="s">
         <v>386</v>
       </c>
-      <c r="E11" s="60" t="s">
+      <c r="E11" s="48" t="s">
         <v>387</v>
       </c>
-      <c r="F11" s="143" t="s">
+      <c r="F11" s="130" t="s">
         <v>388</v>
       </c>
-      <c r="G11" s="140" t="s">
+      <c r="G11" s="127" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="137" t="s">
+      <c r="B12" s="124" t="s">
         <v>377</v>
       </c>
-      <c r="C12" s="138" t="s">
+      <c r="C12" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="D12" s="139" t="s">
+      <c r="D12" s="126" t="s">
         <v>390</v>
       </c>
-      <c r="E12" s="58" t="s">
+      <c r="E12" s="46" t="s">
         <v>283</v>
       </c>
-      <c r="F12" s="139" t="s">
+      <c r="F12" s="126" t="s">
         <v>391</v>
       </c>
-      <c r="G12" s="140" t="s">
+      <c r="G12" s="127" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="141" t="s">
+      <c r="B13" s="128" t="s">
         <v>393</v>
       </c>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="129" t="s">
         <v>394</v>
       </c>
-      <c r="D13" s="143" t="s">
+      <c r="D13" s="130" t="s">
         <v>395</v>
       </c>
-      <c r="E13" s="60" t="s">
+      <c r="E13" s="48" t="s">
         <v>396</v>
       </c>
-      <c r="F13" s="143" t="s">
+      <c r="F13" s="130" t="s">
         <v>397</v>
       </c>
-      <c r="G13" s="140" t="s">
+      <c r="G13" s="127" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="137" t="s">
+      <c r="B14" s="124" t="s">
         <v>393</v>
       </c>
-      <c r="C14" s="138" t="s">
+      <c r="C14" s="125" t="s">
         <v>394</v>
       </c>
-      <c r="D14" s="139" t="s">
+      <c r="D14" s="126" t="s">
         <v>399</v>
       </c>
-      <c r="E14" s="58" t="s">
+      <c r="E14" s="46" t="s">
         <v>400</v>
       </c>
-      <c r="F14" s="139" t="s">
+      <c r="F14" s="126" t="s">
         <v>401</v>
       </c>
-      <c r="G14" s="140" t="s">
+      <c r="G14" s="127" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="141" t="s">
+      <c r="B15" s="128" t="s">
         <v>393</v>
       </c>
-      <c r="C15" s="142" t="s">
+      <c r="C15" s="129" t="s">
         <v>394</v>
       </c>
-      <c r="D15" s="143" t="s">
+      <c r="D15" s="130" t="s">
         <v>403</v>
       </c>
-      <c r="E15" s="60" t="s">
+      <c r="E15" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="F15" s="143" t="s">
+      <c r="F15" s="130" t="s">
         <v>405</v>
       </c>
-      <c r="G15" s="140" t="s">
+      <c r="G15" s="127" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="137" t="s">
+      <c r="B16" s="124" t="s">
         <v>407</v>
       </c>
-      <c r="C16" s="138" t="s">
+      <c r="C16" s="125" t="s">
         <v>394</v>
       </c>
-      <c r="D16" s="139" t="s">
+      <c r="D16" s="126" t="s">
         <v>408</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="E16" s="46" t="s">
         <v>409</v>
       </c>
-      <c r="F16" s="139" t="s">
+      <c r="F16" s="126" t="s">
         <v>410</v>
       </c>
-      <c r="G16" s="140" t="s">
+      <c r="G16" s="127" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="141" t="s">
+      <c r="B17" s="128" t="s">
         <v>407</v>
       </c>
-      <c r="C17" s="142" t="s">
+      <c r="C17" s="129" t="s">
         <v>412</v>
       </c>
-      <c r="D17" s="143" t="s">
+      <c r="D17" s="130" t="s">
         <v>413</v>
       </c>
-      <c r="E17" s="60" t="s">
+      <c r="E17" s="48" t="s">
         <v>414</v>
       </c>
-      <c r="F17" s="143" t="s">
+      <c r="F17" s="130" t="s">
         <v>415</v>
       </c>
-      <c r="G17" s="140" t="s">
+      <c r="G17" s="127" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="137" t="s">
+      <c r="B18" s="124" t="s">
         <v>407</v>
       </c>
-      <c r="C18" s="138" t="s">
+      <c r="C18" s="125" t="s">
         <v>417</v>
       </c>
-      <c r="D18" s="139" t="s">
+      <c r="D18" s="126" t="s">
         <v>418</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F18" s="139" t="s">
+      <c r="F18" s="126" t="s">
         <v>419</v>
       </c>
-      <c r="G18" s="140" t="s">
+      <c r="G18" s="127" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="140" t="s">
         <v>421</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="140"/>
+      <c r="E19" s="140"/>
+      <c r="F19" s="140"/>
+      <c r="G19" s="140"/>
     </row>
     <row r="20" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="137" t="s">
+      <c r="B20" s="124" t="s">
         <v>422</v>
       </c>
-      <c r="C20" s="138" t="s">
+      <c r="C20" s="125" t="s">
         <v>423</v>
       </c>
-      <c r="D20" s="139" t="s">
+      <c r="D20" s="126" t="s">
         <v>424</v>
       </c>
-      <c r="E20" s="58" t="s">
+      <c r="E20" s="46" t="s">
         <v>400</v>
       </c>
-      <c r="F20" s="139" t="s">
+      <c r="F20" s="126" t="s">
         <v>425</v>
       </c>
-      <c r="G20" s="140" t="s">
+      <c r="G20" s="127" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="141" t="s">
+      <c r="B21" s="128" t="s">
         <v>422</v>
       </c>
-      <c r="C21" s="142" t="s">
+      <c r="C21" s="129" t="s">
         <v>423</v>
       </c>
-      <c r="D21" s="143" t="s">
+      <c r="D21" s="130" t="s">
         <v>427</v>
       </c>
-      <c r="E21" s="60" t="s">
+      <c r="E21" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="F21" s="143" t="s">
+      <c r="F21" s="130" t="s">
         <v>428</v>
       </c>
-      <c r="G21" s="140" t="s">
+      <c r="G21" s="127" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="137" t="s">
+      <c r="B22" s="124" t="s">
         <v>430</v>
       </c>
-      <c r="C22" s="138" t="s">
+      <c r="C22" s="125" t="s">
         <v>431</v>
       </c>
-      <c r="D22" s="139" t="s">
+      <c r="D22" s="126" t="s">
         <v>432</v>
       </c>
-      <c r="E22" s="58" t="s">
+      <c r="E22" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F22" s="139" t="s">
+      <c r="F22" s="126" t="s">
         <v>433</v>
       </c>
-      <c r="G22" s="140" t="s">
+      <c r="G22" s="127" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="141" t="s">
+      <c r="B23" s="128" t="s">
         <v>430</v>
       </c>
-      <c r="C23" s="142" t="s">
+      <c r="C23" s="129" t="s">
         <v>435</v>
       </c>
-      <c r="D23" s="143" t="s">
+      <c r="D23" s="130" t="s">
         <v>436</v>
       </c>
-      <c r="E23" s="60" t="s">
+      <c r="E23" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="F23" s="143" t="s">
+      <c r="F23" s="130" t="s">
         <v>437</v>
       </c>
-      <c r="G23" s="140" t="s">
+      <c r="G23" s="127" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="137" t="s">
+      <c r="B24" s="124" t="s">
         <v>430</v>
       </c>
-      <c r="C24" s="138" t="s">
+      <c r="C24" s="125" t="s">
         <v>435</v>
       </c>
-      <c r="D24" s="139" t="s">
+      <c r="D24" s="126" t="s">
         <v>439</v>
       </c>
-      <c r="E24" s="58" t="s">
+      <c r="E24" s="46" t="s">
         <v>440</v>
       </c>
-      <c r="F24" s="139" t="s">
+      <c r="F24" s="126" t="s">
         <v>441</v>
       </c>
-      <c r="G24" s="140" t="s">
+      <c r="G24" s="127" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="141" t="s">
+      <c r="B25" s="128" t="s">
         <v>443</v>
       </c>
-      <c r="C25" s="142" t="s">
+      <c r="C25" s="129" t="s">
         <v>435</v>
       </c>
-      <c r="D25" s="143" t="s">
+      <c r="D25" s="130" t="s">
         <v>444</v>
       </c>
-      <c r="E25" s="60" t="s">
+      <c r="E25" s="48" t="s">
         <v>396</v>
       </c>
-      <c r="F25" s="143" t="s">
+      <c r="F25" s="130" t="s">
         <v>445</v>
       </c>
-      <c r="G25" s="140" t="s">
+      <c r="G25" s="127" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="137" t="s">
+      <c r="B26" s="124" t="s">
         <v>443</v>
       </c>
-      <c r="C26" s="138" t="s">
+      <c r="C26" s="125" t="s">
         <v>435</v>
       </c>
-      <c r="D26" s="139" t="s">
+      <c r="D26" s="126" t="s">
         <v>447</v>
       </c>
-      <c r="E26" s="58" t="s">
+      <c r="E26" s="46" t="s">
         <v>448</v>
       </c>
-      <c r="F26" s="139" t="s">
+      <c r="F26" s="126" t="s">
         <v>449</v>
       </c>
-      <c r="G26" s="140" t="s">
+      <c r="G26" s="127" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="141" t="s">
+      <c r="B27" s="128" t="s">
         <v>451</v>
       </c>
-      <c r="C27" s="142" t="s">
+      <c r="C27" s="129" t="s">
         <v>452</v>
       </c>
-      <c r="D27" s="143" t="s">
+      <c r="D27" s="130" t="s">
         <v>453</v>
       </c>
-      <c r="E27" s="60" t="s">
+      <c r="E27" s="48" t="s">
         <v>454</v>
       </c>
-      <c r="F27" s="143" t="s">
+      <c r="F27" s="130" t="s">
         <v>455</v>
       </c>
-      <c r="G27" s="140" t="s">
+      <c r="G27" s="127" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="140" t="s">
         <v>457</v>
       </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="140"/>
     </row>
     <row r="29" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="141" t="s">
+      <c r="B29" s="128" t="s">
         <v>458</v>
       </c>
-      <c r="C29" s="142" t="s">
+      <c r="C29" s="129" t="s">
         <v>423</v>
       </c>
-      <c r="D29" s="143" t="s">
+      <c r="D29" s="130" t="s">
         <v>459</v>
       </c>
-      <c r="E29" s="60" t="s">
+      <c r="E29" s="48" t="s">
         <v>400</v>
       </c>
-      <c r="F29" s="143" t="s">
+      <c r="F29" s="130" t="s">
         <v>460</v>
       </c>
-      <c r="G29" s="140" t="s">
+      <c r="G29" s="127" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="137" t="s">
+      <c r="B30" s="124" t="s">
         <v>458</v>
       </c>
-      <c r="C30" s="138" t="s">
+      <c r="C30" s="125" t="s">
         <v>462</v>
       </c>
-      <c r="D30" s="139" t="s">
+      <c r="D30" s="126" t="s">
         <v>463</v>
       </c>
-      <c r="E30" s="58" t="s">
+      <c r="E30" s="46" t="s">
         <v>283</v>
       </c>
-      <c r="F30" s="139" t="s">
+      <c r="F30" s="126" t="s">
         <v>464</v>
       </c>
-      <c r="G30" s="140" t="s">
+      <c r="G30" s="127" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="141" t="s">
+      <c r="B31" s="128" t="s">
         <v>466</v>
       </c>
-      <c r="C31" s="142" t="s">
+      <c r="C31" s="129" t="s">
         <v>431</v>
       </c>
-      <c r="D31" s="143" t="s">
+      <c r="D31" s="130" t="s">
         <v>467</v>
       </c>
-      <c r="E31" s="60" t="s">
+      <c r="E31" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="F31" s="143" t="s">
+      <c r="F31" s="130" t="s">
         <v>468</v>
       </c>
-      <c r="G31" s="140" t="s">
+      <c r="G31" s="127" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="137" t="s">
+      <c r="B32" s="124" t="s">
         <v>466</v>
       </c>
-      <c r="C32" s="138" t="s">
+      <c r="C32" s="125" t="s">
         <v>431</v>
       </c>
-      <c r="D32" s="139" t="s">
+      <c r="D32" s="126" t="s">
         <v>470</v>
       </c>
-      <c r="E32" s="58" t="s">
+      <c r="E32" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F32" s="139" t="s">
+      <c r="F32" s="126" t="s">
         <v>471</v>
       </c>
-      <c r="G32" s="140" t="s">
+      <c r="G32" s="127" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="141" t="s">
+      <c r="B33" s="128" t="s">
         <v>473</v>
       </c>
-      <c r="C33" s="142" t="s">
+      <c r="C33" s="129" t="s">
         <v>474</v>
       </c>
-      <c r="D33" s="143" t="s">
+      <c r="D33" s="130" t="s">
         <v>475</v>
       </c>
-      <c r="E33" s="60" t="s">
+      <c r="E33" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="F33" s="143" t="s">
+      <c r="F33" s="130" t="s">
         <v>476</v>
       </c>
-      <c r="G33" s="140" t="s">
+      <c r="G33" s="127" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="137" t="s">
+      <c r="B34" s="124" t="s">
         <v>473</v>
       </c>
-      <c r="C34" s="138" t="s">
+      <c r="C34" s="125" t="s">
         <v>435</v>
       </c>
-      <c r="D34" s="139" t="s">
+      <c r="D34" s="126" t="s">
         <v>478</v>
       </c>
-      <c r="E34" s="58" t="s">
+      <c r="E34" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F34" s="139" t="s">
+      <c r="F34" s="126" t="s">
         <v>479</v>
       </c>
-      <c r="G34" s="140" t="s">
+      <c r="G34" s="127" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="141" t="s">
+      <c r="B35" s="128" t="s">
         <v>481</v>
       </c>
-      <c r="C35" s="142" t="s">
+      <c r="C35" s="129" t="s">
         <v>482</v>
       </c>
-      <c r="D35" s="143" t="s">
+      <c r="D35" s="130" t="s">
         <v>483</v>
       </c>
-      <c r="E35" s="60" t="s">
+      <c r="E35" s="48" t="s">
         <v>484</v>
       </c>
-      <c r="F35" s="143" t="s">
+      <c r="F35" s="130" t="s">
         <v>485</v>
       </c>
-      <c r="G35" s="140" t="s">
+      <c r="G35" s="127" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="137" t="s">
+      <c r="B36" s="124" t="s">
         <v>481</v>
       </c>
-      <c r="C36" s="138" t="s">
+      <c r="C36" s="125" t="s">
         <v>482</v>
       </c>
-      <c r="D36" s="139" t="s">
+      <c r="D36" s="126" t="s">
         <v>487</v>
       </c>
-      <c r="E36" s="58" t="s">
+      <c r="E36" s="46" t="s">
         <v>440</v>
       </c>
-      <c r="F36" s="139" t="s">
+      <c r="F36" s="126" t="s">
         <v>488</v>
       </c>
-      <c r="G36" s="140" t="s">
+      <c r="G36" s="127" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="141" t="s">
+      <c r="B37" s="128" t="s">
         <v>481</v>
       </c>
-      <c r="C37" s="142" t="s">
+      <c r="C37" s="129" t="s">
         <v>482</v>
       </c>
-      <c r="D37" s="143" t="s">
+      <c r="D37" s="130" t="s">
         <v>490</v>
       </c>
-      <c r="E37" s="60" t="s">
+      <c r="E37" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="F37" s="143" t="s">
+      <c r="F37" s="130" t="s">
         <v>491</v>
       </c>
-      <c r="G37" s="140" t="s">
+      <c r="G37" s="127" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="137" t="s">
+      <c r="B38" s="124" t="s">
         <v>481</v>
       </c>
-      <c r="C38" s="138" t="s">
+      <c r="C38" s="125" t="s">
         <v>493</v>
       </c>
-      <c r="D38" s="139" t="s">
+      <c r="D38" s="126" t="s">
         <v>494</v>
       </c>
-      <c r="E38" s="58" t="s">
+      <c r="E38" s="46" t="s">
         <v>387</v>
       </c>
-      <c r="F38" s="139" t="s">
+      <c r="F38" s="126" t="s">
         <v>495</v>
       </c>
-      <c r="G38" s="140" t="s">
+      <c r="G38" s="127" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="140" t="s">
         <v>497</v>
       </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
+      <c r="C39" s="140"/>
+      <c r="D39" s="140"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="140"/>
     </row>
     <row r="40" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="137" t="s">
+      <c r="B40" s="124" t="s">
         <v>498</v>
       </c>
-      <c r="C40" s="138" t="s">
+      <c r="C40" s="125" t="s">
         <v>499</v>
       </c>
-      <c r="D40" s="139" t="s">
+      <c r="D40" s="126" t="s">
         <v>500</v>
       </c>
-      <c r="E40" s="58" t="s">
+      <c r="E40" s="46" t="s">
         <v>396</v>
       </c>
-      <c r="F40" s="139" t="s">
+      <c r="F40" s="126" t="s">
         <v>501</v>
       </c>
-      <c r="G40" s="140" t="s">
+      <c r="G40" s="127" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="141" t="s">
+      <c r="B41" s="128" t="s">
         <v>498</v>
       </c>
-      <c r="C41" s="142" t="s">
+      <c r="C41" s="129" t="s">
         <v>499</v>
       </c>
-      <c r="D41" s="143" t="s">
+      <c r="D41" s="130" t="s">
         <v>503</v>
       </c>
-      <c r="E41" s="60" t="s">
+      <c r="E41" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="F41" s="143" t="s">
+      <c r="F41" s="130" t="s">
         <v>504</v>
       </c>
-      <c r="G41" s="140" t="s">
+      <c r="G41" s="127" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="137" t="s">
+      <c r="B42" s="124" t="s">
         <v>498</v>
       </c>
-      <c r="C42" s="138" t="s">
+      <c r="C42" s="125" t="s">
         <v>435</v>
       </c>
-      <c r="D42" s="139" t="s">
+      <c r="D42" s="126" t="s">
         <v>506</v>
       </c>
-      <c r="E42" s="58" t="s">
+      <c r="E42" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F42" s="139" t="s">
+      <c r="F42" s="126" t="s">
         <v>507</v>
       </c>
-      <c r="G42" s="140" t="s">
+      <c r="G42" s="127" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="141" t="s">
+      <c r="B43" s="128" t="s">
         <v>509</v>
       </c>
-      <c r="C43" s="142" t="s">
+      <c r="C43" s="129" t="s">
         <v>482</v>
       </c>
-      <c r="D43" s="143" t="s">
+      <c r="D43" s="130" t="s">
         <v>510</v>
       </c>
-      <c r="E43" s="60" t="s">
+      <c r="E43" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="F43" s="143" t="s">
+      <c r="F43" s="130" t="s">
         <v>511</v>
       </c>
-      <c r="G43" s="140" t="s">
+      <c r="G43" s="127" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="44" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="140" t="s">
         <v>513</v>
       </c>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
+      <c r="C44" s="140"/>
+      <c r="D44" s="140"/>
+      <c r="E44" s="140"/>
+      <c r="F44" s="140"/>
+      <c r="G44" s="140"/>
     </row>
     <row r="45" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="141" t="s">
+      <c r="B45" s="128" t="s">
         <v>509</v>
       </c>
-      <c r="C45" s="142" t="s">
+      <c r="C45" s="129" t="s">
         <v>499</v>
       </c>
-      <c r="D45" s="143" t="s">
+      <c r="D45" s="130" t="s">
         <v>514</v>
       </c>
-      <c r="E45" s="60" t="s">
+      <c r="E45" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="F45" s="143" t="s">
+      <c r="F45" s="130" t="s">
         <v>515</v>
       </c>
-      <c r="G45" s="140" t="s">
+      <c r="G45" s="127" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="46" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="137" t="s">
+      <c r="B46" s="124" t="s">
         <v>517</v>
       </c>
-      <c r="C46" s="138" t="s">
+      <c r="C46" s="125" t="s">
         <v>499</v>
       </c>
-      <c r="D46" s="139" t="s">
+      <c r="D46" s="126" t="s">
         <v>518</v>
       </c>
-      <c r="E46" s="58" t="s">
+      <c r="E46" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F46" s="139" t="s">
+      <c r="F46" s="126" t="s">
         <v>519</v>
       </c>
-      <c r="G46" s="140" t="s">
+      <c r="G46" s="127" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="47" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="141" t="s">
+      <c r="B47" s="128" t="s">
         <v>517</v>
       </c>
-      <c r="C47" s="142" t="s">
+      <c r="C47" s="129" t="s">
         <v>482</v>
       </c>
-      <c r="D47" s="143" t="s">
+      <c r="D47" s="130" t="s">
         <v>521</v>
       </c>
-      <c r="E47" s="60" t="s">
+      <c r="E47" s="48" t="s">
         <v>522</v>
       </c>
-      <c r="F47" s="143" t="s">
+      <c r="F47" s="130" t="s">
         <v>523</v>
       </c>
-      <c r="G47" s="140" t="s">
+      <c r="G47" s="127" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="140" t="s">
         <v>525</v>
       </c>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
+      <c r="C48" s="140"/>
+      <c r="D48" s="140"/>
+      <c r="E48" s="140"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="140"/>
     </row>
     <row r="49" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="141" t="s">
+      <c r="B49" s="128" t="s">
         <v>526</v>
       </c>
-      <c r="C49" s="142" t="s">
+      <c r="C49" s="129" t="s">
         <v>499</v>
       </c>
-      <c r="D49" s="143" t="s">
+      <c r="D49" s="130" t="s">
         <v>527</v>
       </c>
-      <c r="E49" s="60" t="s">
+      <c r="E49" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="F49" s="143" t="s">
+      <c r="F49" s="130" t="s">
         <v>528</v>
       </c>
-      <c r="G49" s="140" t="s">
+      <c r="G49" s="127" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="137" t="s">
+      <c r="B50" s="124" t="s">
         <v>526</v>
       </c>
-      <c r="C50" s="138" t="s">
+      <c r="C50" s="125" t="s">
         <v>499</v>
       </c>
-      <c r="D50" s="139" t="s">
+      <c r="D50" s="126" t="s">
         <v>530</v>
       </c>
-      <c r="E50" s="58" t="s">
+      <c r="E50" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F50" s="139" t="s">
+      <c r="F50" s="126" t="s">
         <v>531</v>
       </c>
-      <c r="G50" s="140" t="s">
+      <c r="G50" s="127" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="141" t="s">
+      <c r="B51" s="128" t="s">
         <v>533</v>
       </c>
-      <c r="C51" s="142" t="s">
+      <c r="C51" s="129" t="s">
         <v>499</v>
       </c>
-      <c r="D51" s="143" t="s">
+      <c r="D51" s="130" t="s">
         <v>534</v>
       </c>
-      <c r="E51" s="60" t="s">
+      <c r="E51" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="F51" s="143" t="s">
+      <c r="F51" s="130" t="s">
         <v>535</v>
       </c>
-      <c r="G51" s="140" t="s">
+      <c r="G51" s="127" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="52" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="137" t="s">
+      <c r="B52" s="124" t="s">
         <v>533</v>
       </c>
-      <c r="C52" s="138" t="s">
+      <c r="C52" s="125" t="s">
         <v>482</v>
       </c>
-      <c r="D52" s="139" t="s">
+      <c r="D52" s="126" t="s">
         <v>537</v>
       </c>
-      <c r="E52" s="58" t="s">
+      <c r="E52" s="46" t="s">
         <v>522</v>
       </c>
-      <c r="F52" s="139" t="s">
+      <c r="F52" s="126" t="s">
         <v>538</v>
       </c>
-      <c r="G52" s="140" t="s">
+      <c r="G52" s="127" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="140" t="s">
         <v>540</v>
       </c>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
+      <c r="C53" s="140"/>
+      <c r="D53" s="140"/>
+      <c r="E53" s="140"/>
+      <c r="F53" s="140"/>
+      <c r="G53" s="140"/>
     </row>
     <row r="54" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="137" t="s">
+      <c r="B54" s="124" t="s">
         <v>541</v>
       </c>
-      <c r="C54" s="138" t="s">
+      <c r="C54" s="125" t="s">
         <v>499</v>
       </c>
-      <c r="D54" s="139" t="s">
+      <c r="D54" s="126" t="s">
         <v>542</v>
       </c>
-      <c r="E54" s="58" t="s">
+      <c r="E54" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F54" s="139" t="s">
+      <c r="F54" s="126" t="s">
         <v>543</v>
       </c>
-      <c r="G54" s="140" t="s">
+      <c r="G54" s="127" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="141" t="s">
+      <c r="B55" s="128" t="s">
         <v>541</v>
       </c>
-      <c r="C55" s="142" t="s">
+      <c r="C55" s="129" t="s">
         <v>499</v>
       </c>
-      <c r="D55" s="143" t="s">
+      <c r="D55" s="130" t="s">
         <v>544</v>
       </c>
-      <c r="E55" s="60" t="s">
+      <c r="E55" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="F55" s="143" t="s">
+      <c r="F55" s="130" t="s">
         <v>545</v>
       </c>
-      <c r="G55" s="140" t="s">
+      <c r="G55" s="127" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="56" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="137" t="s">
+      <c r="B56" s="124" t="s">
         <v>547</v>
       </c>
-      <c r="C56" s="138" t="s">
+      <c r="C56" s="125" t="s">
         <v>499</v>
       </c>
-      <c r="D56" s="139" t="s">
+      <c r="D56" s="126" t="s">
         <v>548</v>
       </c>
-      <c r="E56" s="58" t="s">
+      <c r="E56" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F56" s="139" t="s">
+      <c r="F56" s="126" t="s">
         <v>549</v>
       </c>
-      <c r="G56" s="140" t="s">
+      <c r="G56" s="127" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="57" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="141" t="s">
+      <c r="B57" s="128" t="s">
         <v>547</v>
       </c>
-      <c r="C57" s="142" t="s">
+      <c r="C57" s="129" t="s">
         <v>435</v>
       </c>
-      <c r="D57" s="143" t="s">
+      <c r="D57" s="130" t="s">
         <v>551</v>
       </c>
-      <c r="E57" s="60" t="s">
+      <c r="E57" s="48" t="s">
         <v>552</v>
       </c>
-      <c r="F57" s="143" t="s">
+      <c r="F57" s="130" t="s">
         <v>553</v>
       </c>
-      <c r="G57" s="140" t="s">
+      <c r="G57" s="127" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="58" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="137" t="s">
+      <c r="B58" s="124" t="s">
         <v>555</v>
       </c>
-      <c r="C58" s="138" t="s">
+      <c r="C58" s="125" t="s">
         <v>482</v>
       </c>
-      <c r="D58" s="139" t="s">
+      <c r="D58" s="126" t="s">
         <v>556</v>
       </c>
-      <c r="E58" s="58" t="s">
+      <c r="E58" s="46" t="s">
         <v>404</v>
       </c>
-      <c r="F58" s="139" t="s">
+      <c r="F58" s="126" t="s">
         <v>557</v>
       </c>
-      <c r="G58" s="140" t="s">
+      <c r="G58" s="127" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="59" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="140" t="s">
         <v>559</v>
       </c>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
+      <c r="C59" s="140"/>
+      <c r="D59" s="140"/>
+      <c r="E59" s="140"/>
+      <c r="F59" s="140"/>
+      <c r="G59" s="140"/>
     </row>
     <row r="60" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="137" t="s">
+      <c r="B60" s="124" t="s">
         <v>560</v>
       </c>
-      <c r="C60" s="138" t="s">
+      <c r="C60" s="125" t="s">
         <v>499</v>
       </c>
-      <c r="D60" s="139" t="s">
+      <c r="D60" s="126" t="s">
         <v>561</v>
       </c>
-      <c r="E60" s="58" t="s">
+      <c r="E60" s="46" t="s">
         <v>283</v>
       </c>
-      <c r="F60" s="139" t="s">
+      <c r="F60" s="126" t="s">
         <v>562</v>
       </c>
-      <c r="G60" s="140" t="s">
+      <c r="G60" s="127" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="61" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="141" t="s">
+      <c r="B61" s="128" t="s">
         <v>560</v>
       </c>
-      <c r="C61" s="142" t="s">
+      <c r="C61" s="129" t="s">
         <v>499</v>
       </c>
-      <c r="D61" s="143" t="s">
+      <c r="D61" s="130" t="s">
         <v>564</v>
       </c>
-      <c r="E61" s="60" t="s">
+      <c r="E61" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="F61" s="143" t="s">
+      <c r="F61" s="130" t="s">
         <v>565</v>
       </c>
-      <c r="G61" s="140" t="s">
+      <c r="G61" s="127" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="137" t="s">
+      <c r="B62" s="124" t="s">
         <v>567</v>
       </c>
-      <c r="C62" s="138" t="s">
+      <c r="C62" s="125" t="s">
         <v>482</v>
       </c>
-      <c r="D62" s="139" t="s">
+      <c r="D62" s="126" t="s">
         <v>568</v>
       </c>
-      <c r="E62" s="58" t="s">
+      <c r="E62" s="46" t="s">
         <v>404</v>
       </c>
-      <c r="F62" s="139" t="s">
+      <c r="F62" s="126" t="s">
         <v>569</v>
       </c>
-      <c r="G62" s="140" t="s">
+      <c r="G62" s="127" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="140" t="s">
         <v>571</v>
       </c>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
+      <c r="C63" s="140"/>
+      <c r="D63" s="140"/>
+      <c r="E63" s="140"/>
+      <c r="F63" s="140"/>
+      <c r="G63" s="140"/>
     </row>
     <row r="64" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="137" t="s">
+      <c r="B64" s="124" t="s">
         <v>572</v>
       </c>
-      <c r="C64" s="138" t="s">
+      <c r="C64" s="125" t="s">
         <v>435</v>
       </c>
-      <c r="D64" s="139" t="s">
+      <c r="D64" s="126" t="s">
         <v>573</v>
       </c>
-      <c r="E64" s="58" t="s">
+      <c r="E64" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F64" s="139" t="s">
+      <c r="F64" s="126" t="s">
         <v>574</v>
       </c>
-      <c r="G64" s="140" t="s">
+      <c r="G64" s="127" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="141" t="s">
+      <c r="B65" s="128" t="s">
         <v>572</v>
       </c>
-      <c r="C65" s="142" t="s">
+      <c r="C65" s="129" t="s">
         <v>435</v>
       </c>
-      <c r="D65" s="143" t="s">
+      <c r="D65" s="130" t="s">
         <v>576</v>
       </c>
-      <c r="E65" s="60" t="s">
+      <c r="E65" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="F65" s="143" t="s">
+      <c r="F65" s="130" t="s">
         <v>577</v>
       </c>
-      <c r="G65" s="140" t="s">
+      <c r="G65" s="127" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="137" t="s">
+      <c r="B66" s="124" t="s">
         <v>572</v>
       </c>
-      <c r="C66" s="138" t="s">
+      <c r="C66" s="125" t="s">
         <v>365</v>
       </c>
-      <c r="D66" s="139" t="s">
+      <c r="D66" s="126" t="s">
         <v>579</v>
       </c>
-      <c r="E66" s="58" t="s">
+      <c r="E66" s="46" t="s">
         <v>295</v>
       </c>
-      <c r="F66" s="139" t="s">
+      <c r="F66" s="126" t="s">
         <v>580</v>
       </c>
-      <c r="G66" s="140" t="s">
+      <c r="G66" s="127" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="140" t="s">
         <v>582</v>
       </c>
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
+      <c r="C67" s="140"/>
+      <c r="D67" s="140"/>
+      <c r="E67" s="140"/>
+      <c r="F67" s="140"/>
+      <c r="G67" s="140"/>
     </row>
     <row r="68" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="137" t="s">
+      <c r="B68" s="124" t="s">
         <v>583</v>
       </c>
-      <c r="C68" s="138" t="s">
+      <c r="C68" s="125" t="s">
         <v>381</v>
       </c>
-      <c r="D68" s="139" t="s">
+      <c r="D68" s="126" t="s">
         <v>584</v>
       </c>
-      <c r="E68" s="58" t="s">
+      <c r="E68" s="46" t="s">
         <v>283</v>
       </c>
-      <c r="F68" s="139" t="s">
+      <c r="F68" s="126" t="s">
         <v>585</v>
       </c>
-      <c r="G68" s="140" t="s">
+      <c r="G68" s="127" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="69" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="141" t="s">
+      <c r="B69" s="128" t="s">
         <v>583</v>
       </c>
-      <c r="C69" s="142" t="s">
+      <c r="C69" s="129" t="s">
         <v>587</v>
       </c>
-      <c r="D69" s="143" t="s">
+      <c r="D69" s="130" t="s">
         <v>588</v>
       </c>
-      <c r="E69" s="60" t="s">
+      <c r="E69" s="48" t="s">
         <v>589</v>
       </c>
-      <c r="F69" s="143" t="s">
+      <c r="F69" s="130" t="s">
         <v>590</v>
       </c>
-      <c r="G69" s="140" t="s">
+      <c r="G69" s="127" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="70" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="137" t="s">
+      <c r="B70" s="124" t="s">
         <v>583</v>
       </c>
-      <c r="C70" s="138" t="s">
+      <c r="C70" s="125" t="s">
         <v>592</v>
       </c>
-      <c r="D70" s="139" t="s">
+      <c r="D70" s="126" t="s">
         <v>593</v>
       </c>
-      <c r="E70" s="58" t="s">
+      <c r="E70" s="46" t="s">
         <v>283</v>
       </c>
-      <c r="F70" s="139" t="s">
+      <c r="F70" s="126" t="s">
         <v>594</v>
       </c>
-      <c r="G70" s="140" t="s">
+      <c r="G70" s="127" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="71" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="140" t="s">
         <v>596</v>
       </c>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
+      <c r="C71" s="140"/>
+      <c r="D71" s="140"/>
+      <c r="E71" s="140"/>
+      <c r="F71" s="140"/>
+      <c r="G71" s="140"/>
     </row>
     <row r="72" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="137" t="s">
+      <c r="B72" s="124" t="s">
         <v>597</v>
       </c>
-      <c r="C72" s="138" t="s">
+      <c r="C72" s="125" t="s">
         <v>365</v>
       </c>
-      <c r="D72" s="139" t="s">
+      <c r="D72" s="126" t="s">
         <v>598</v>
       </c>
-      <c r="E72" s="58" t="s">
+      <c r="E72" s="46" t="s">
         <v>295</v>
       </c>
-      <c r="F72" s="139" t="s">
+      <c r="F72" s="126" t="s">
         <v>599</v>
       </c>
-      <c r="G72" s="140" t="s">
+      <c r="G72" s="127" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="73" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="141" t="s">
+      <c r="B73" s="128" t="s">
         <v>597</v>
       </c>
-      <c r="C73" s="142" t="s">
+      <c r="C73" s="129" t="s">
         <v>365</v>
       </c>
-      <c r="D73" s="143" t="s">
+      <c r="D73" s="130" t="s">
         <v>601</v>
       </c>
-      <c r="E73" s="60" t="s">
+      <c r="E73" s="48" t="s">
         <v>602</v>
       </c>
-      <c r="F73" s="143" t="s">
+      <c r="F73" s="130" t="s">
         <v>603</v>
       </c>
-      <c r="G73" s="140" t="s">
+      <c r="G73" s="127" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="74" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="137" t="s">
+      <c r="B74" s="124" t="s">
         <v>597</v>
       </c>
-      <c r="C74" s="138" t="s">
+      <c r="C74" s="125" t="s">
         <v>605</v>
       </c>
-      <c r="D74" s="139" t="s">
+      <c r="D74" s="126" t="s">
         <v>606</v>
       </c>
-      <c r="E74" s="58" t="s">
+      <c r="E74" s="46" t="s">
         <v>283</v>
       </c>
-      <c r="F74" s="139" t="s">
+      <c r="F74" s="126" t="s">
         <v>607</v>
       </c>
-      <c r="G74" s="140" t="s">
+      <c r="G74" s="127" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="75" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="141" t="s">
+      <c r="B75" s="128" t="s">
         <v>609</v>
       </c>
-      <c r="C75" s="142" t="s">
+      <c r="C75" s="129" t="s">
         <v>610</v>
       </c>
-      <c r="D75" s="143" t="s">
+      <c r="D75" s="130" t="s">
         <v>611</v>
       </c>
-      <c r="E75" s="60" t="s">
+      <c r="E75" s="48" t="s">
         <v>387</v>
       </c>
-      <c r="F75" s="143" t="s">
+      <c r="F75" s="130" t="s">
         <v>612</v>
       </c>
-      <c r="G75" s="140" t="s">
+      <c r="G75" s="127" t="s">
         <v>613</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B39:G39"/>
     <mergeCell ref="B67:G67"/>
     <mergeCell ref="B71:G71"/>
     <mergeCell ref="B44:G44"/>
@@ -7253,11 +7262,6 @@
     <mergeCell ref="B53:G53"/>
     <mergeCell ref="B59:G59"/>
     <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B39:G39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7279,240 +7283,240 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="145" t="s">
         <v>614</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
     </row>
     <row r="4" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="140" t="s">
         <v>615</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="14" t="s">
         <v>616</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="14" t="s">
         <v>617</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="14" t="s">
         <v>618</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="14" t="s">
         <v>619</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="14" t="s">
         <v>620</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="14" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="27" t="s">
         <v>621</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="31">
         <v>10716.34</v>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="31">
         <v>479.77352991420003</v>
       </c>
-      <c r="E6" s="144">
+      <c r="E6" s="131">
         <v>10236.5664700858</v>
       </c>
-      <c r="F6" s="144">
+      <c r="F6" s="131">
         <v>122838.79764103</v>
       </c>
-      <c r="G6" s="58" t="s">
+      <c r="G6" s="46" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="21" t="s">
         <v>623</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="25">
         <v>900</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="25">
         <v>0</v>
       </c>
-      <c r="E7" s="65">
+      <c r="E7" s="52">
         <v>900</v>
       </c>
-      <c r="F7" s="65">
+      <c r="F7" s="52">
         <v>10800</v>
       </c>
-      <c r="G7" s="60" t="s">
+      <c r="G7" s="48" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="27" t="s">
         <v>625</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="31">
         <v>0</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="31">
         <v>520</v>
       </c>
-      <c r="E8" s="145">
+      <c r="E8" s="132">
         <v>-520</v>
       </c>
-      <c r="F8" s="145">
+      <c r="F8" s="132">
         <v>-6240</v>
       </c>
-      <c r="G8" s="58" t="s">
+      <c r="G8" s="46" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="21" t="s">
         <v>627</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="25">
         <v>0</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="25">
         <v>48</v>
       </c>
-      <c r="E9" s="146">
+      <c r="E9" s="133">
         <v>-48</v>
       </c>
-      <c r="F9" s="146">
+      <c r="F9" s="133">
         <v>-576</v>
       </c>
-      <c r="G9" s="60" t="s">
+      <c r="G9" s="48" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="27" t="s">
         <v>629</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="31">
         <v>0</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="31">
         <v>80</v>
       </c>
-      <c r="E10" s="145">
+      <c r="E10" s="132">
         <v>-80</v>
       </c>
-      <c r="F10" s="145">
+      <c r="F10" s="132">
         <v>-960</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="46" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="147">
+      <c r="C11" s="134">
         <v>11616.34</v>
       </c>
-      <c r="D11" s="147">
+      <c r="D11" s="134">
         <v>1127.7735299142</v>
       </c>
-      <c r="E11" s="148">
+      <c r="E11" s="135">
         <v>10488.5664700858</v>
       </c>
-      <c r="F11" s="148">
+      <c r="F11" s="135">
         <v>125862.79764103</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="1" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="143" t="s">
         <v>632</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="143"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="143"/>
     </row>
     <row r="14" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="144" t="s">
         <v>633</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="C14" s="144"/>
+      <c r="D14" s="144"/>
+      <c r="E14" s="144"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="144"/>
     </row>
     <row r="16" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="140" t="s">
         <v>206</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="140"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="140"/>
+      <c r="G16" s="140"/>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="27" t="s">
         <v>634</v>
       </c>
-      <c r="C17" s="149">
+      <c r="C17" s="136">
         <v>45502.761803763002</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="21" t="s">
         <v>635</v>
       </c>
-      <c r="C18" s="150">
+      <c r="C18" s="137">
         <v>10488.5664700858</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="27" t="s">
         <v>636</v>
       </c>
-      <c r="C19" s="151">
+      <c r="C19" s="138">
         <v>125862.79764103</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="21" t="s">
         <v>637</v>
       </c>
-      <c r="C20" s="152">
+      <c r="C20" s="139">
         <v>4.3383203923567999</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="27" t="s">
         <v>638</v>
       </c>
-      <c r="C21" s="151">
+      <c r="C21" s="138">
         <v>80360.035837266594</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="21" t="s">
         <v>639</v>
       </c>
-      <c r="C22" s="150">
+      <c r="C22" s="137">
         <v>332085.63111932599</v>
       </c>
     </row>
